--- a/src/download/dist1.xlsx
+++ b/src/download/dist1.xlsx
@@ -1316,7 +1316,7 @@
     <row r="2" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>填报日期：2025年03月19日 19时</t>
+          <t>填报日期：2025年03月19日 20时</t>
         </is>
       </c>
       <c r="B2" s="7" t="n"/>

--- a/src/download/dist1.xlsx
+++ b/src/download/dist1.xlsx
@@ -1316,7 +1316,7 @@
     <row r="2" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>填报日期：2025年03月19日 20时</t>
+          <t>填报日期：2025年03月20日 15时</t>
         </is>
       </c>
       <c r="B2" s="7" t="n"/>
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="D5" s="33" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E5" s="33" t="n">
         <v>5.71</v>
       </c>
-      <c r="E5" s="33" t="n">
-        <v>5.62</v>
-      </c>
       <c r="F5" s="34" t="n">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>5.99</v>
+        <v>5.89</v>
       </c>
       <c r="H5" s="35">
         <f>D5-E5</f>
@@ -1475,16 +1475,16 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="E6" s="33" t="n">
         <v>4.66</v>
       </c>
-      <c r="E6" s="33" t="n">
-        <v>4.52</v>
-      </c>
       <c r="F6" s="34" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="G6" s="34" t="n">
-        <v>4.79</v>
+        <v>4.7</v>
       </c>
       <c r="H6" s="35">
         <f>D6-E6</f>
@@ -1515,16 +1515,16 @@
         </is>
       </c>
       <c r="D7" s="33" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="E7" s="33" t="n">
         <v>4.76</v>
       </c>
-      <c r="E7" s="33" t="n">
-        <v>4.63</v>
-      </c>
       <c r="F7" s="34" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="G7" s="34" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="H7" s="35">
         <f>D7-E7</f>
@@ -1555,16 +1555,16 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="E8" s="33" t="n">
         <v>4.15</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>4.13</v>
       </c>
       <c r="F8" s="34" t="n">
         <v>3.96</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>5.3</v>
+        <v>5.44</v>
       </c>
       <c r="H8" s="35">
         <f>D8-E8</f>
@@ -1595,16 +1595,16 @@
         </is>
       </c>
       <c r="D9" s="33" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="E9" s="33" t="n">
         <v>4.76</v>
       </c>
-      <c r="E9" s="33" t="n">
-        <v>4.63</v>
-      </c>
       <c r="F9" s="34" t="n">
-        <v>3.94</v>
+        <v>3.99</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>4.7</v>
+        <v>4.75</v>
       </c>
       <c r="H9" s="35">
         <f>D9-E9</f>
@@ -1635,16 +1635,16 @@
         </is>
       </c>
       <c r="D10" s="33" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E10" s="33" t="n">
         <v>8.34</v>
       </c>
-      <c r="E10" s="33" t="n">
-        <v>8.460000000000001</v>
-      </c>
       <c r="F10" s="34" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>8.359999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="H10" s="35">
         <f>D10-E10</f>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D11" s="33" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="E11" s="33" t="n">
         <v>7.19</v>
       </c>
-      <c r="E11" s="33" t="n">
-        <v>7.2</v>
-      </c>
       <c r="F11" s="34" t="n">
-        <v>7.29</v>
+        <v>7.25</v>
       </c>
       <c r="G11" s="34" t="n">
         <v>7.59</v>
@@ -1715,16 +1715,16 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E12" s="33" t="n">
         <v>5.71</v>
       </c>
-      <c r="E12" s="33" t="n">
-        <v>5.62</v>
-      </c>
       <c r="F12" s="34" t="n">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>5.99</v>
+        <v>5.89</v>
       </c>
       <c r="H12" s="35">
         <f>D12-E12</f>
@@ -1755,16 +1755,16 @@
         </is>
       </c>
       <c r="D13" s="33" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E13" s="33" t="n">
         <v>5.71</v>
       </c>
-      <c r="E13" s="33" t="n">
-        <v>5.62</v>
-      </c>
       <c r="F13" s="34" t="n">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>5.99</v>
+        <v>5.89</v>
       </c>
       <c r="H13" s="35">
         <f>D13-E13</f>
@@ -1795,16 +1795,16 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E14" s="33" t="n">
         <v>5.71</v>
       </c>
-      <c r="E14" s="33" t="n">
-        <v>5.62</v>
-      </c>
       <c r="F14" s="34" t="n">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>5.99</v>
+        <v>5.89</v>
       </c>
       <c r="H14" s="35">
         <f>D14-E14</f>

--- a/src/download/dist1.xlsx
+++ b/src/download/dist1.xlsx
@@ -1316,7 +1316,7 @@
     <row r="2" ht="14.25" customFormat="1" customHeight="1" s="7">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>填报日期：2025年03月20日 15时</t>
+          <t>填报日期：2025年03月21日 19时</t>
         </is>
       </c>
       <c r="B2" s="7" t="n"/>
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="D5" s="33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E5" s="33" t="n">
         <v>5.74</v>
       </c>
-      <c r="E5" s="33" t="n">
-        <v>5.71</v>
-      </c>
       <c r="F5" s="34" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="G5" s="34" t="n">
-        <v>5.89</v>
+        <v>5.72</v>
       </c>
       <c r="H5" s="35">
         <f>D5-E5</f>
@@ -1475,16 +1475,16 @@
         </is>
       </c>
       <c r="D6" s="33" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="E6" s="33" t="n">
         <v>4.67</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="F6" s="34" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="G6" s="34" t="n">
         <v>4.66</v>
-      </c>
-      <c r="F6" s="34" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="G6" s="34" t="n">
-        <v>4.7</v>
       </c>
       <c r="H6" s="35">
         <f>D6-E6</f>
@@ -1515,16 +1515,16 @@
         </is>
       </c>
       <c r="D7" s="33" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E7" s="33" t="n">
         <v>4.79</v>
       </c>
-      <c r="E7" s="33" t="n">
-        <v>4.76</v>
-      </c>
       <c r="F7" s="34" t="n">
-        <v>3.99</v>
+        <v>4.17</v>
       </c>
       <c r="G7" s="34" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="H7" s="35">
         <f>D7-E7</f>
@@ -1555,16 +1555,16 @@
         </is>
       </c>
       <c r="D8" s="33" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E8" s="33" t="n">
         <v>4.18</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>4.15</v>
       </c>
       <c r="F8" s="34" t="n">
         <v>3.96</v>
       </c>
       <c r="G8" s="34" t="n">
-        <v>5.44</v>
+        <v>5.55</v>
       </c>
       <c r="H8" s="35">
         <f>D8-E8</f>
@@ -1595,16 +1595,16 @@
         </is>
       </c>
       <c r="D9" s="33" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E9" s="33" t="n">
         <v>4.79</v>
       </c>
-      <c r="E9" s="33" t="n">
-        <v>4.76</v>
-      </c>
       <c r="F9" s="34" t="n">
-        <v>3.99</v>
+        <v>4.17</v>
       </c>
       <c r="G9" s="34" t="n">
-        <v>4.75</v>
+        <v>4.73</v>
       </c>
       <c r="H9" s="35">
         <f>D9-E9</f>
@@ -1635,16 +1635,16 @@
         </is>
       </c>
       <c r="D10" s="33" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="E10" s="33" t="n">
         <v>8.25</v>
       </c>
-      <c r="E10" s="33" t="n">
-        <v>8.34</v>
-      </c>
       <c r="F10" s="34" t="n">
-        <v>8.619999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="G10" s="34" t="n">
-        <v>8.31</v>
+        <v>8.33</v>
       </c>
       <c r="H10" s="35">
         <f>D10-E10</f>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="D11" s="33" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="E11" s="33" t="n">
         <v>7.18</v>
       </c>
-      <c r="E11" s="33" t="n">
-        <v>7.19</v>
-      </c>
       <c r="F11" s="34" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="G11" s="34" t="n">
         <v>7.59</v>
@@ -1715,16 +1715,16 @@
         </is>
       </c>
       <c r="D12" s="33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E12" s="33" t="n">
         <v>5.74</v>
       </c>
-      <c r="E12" s="33" t="n">
-        <v>5.71</v>
-      </c>
       <c r="F12" s="34" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="G12" s="34" t="n">
-        <v>5.89</v>
+        <v>5.72</v>
       </c>
       <c r="H12" s="35">
         <f>D12-E12</f>
@@ -1755,16 +1755,16 @@
         </is>
       </c>
       <c r="D13" s="33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E13" s="33" t="n">
         <v>5.74</v>
       </c>
-      <c r="E13" s="33" t="n">
-        <v>5.71</v>
-      </c>
       <c r="F13" s="34" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="G13" s="34" t="n">
-        <v>5.89</v>
+        <v>5.72</v>
       </c>
       <c r="H13" s="35">
         <f>D13-E13</f>
@@ -1795,16 +1795,16 @@
         </is>
       </c>
       <c r="D14" s="33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E14" s="33" t="n">
         <v>5.74</v>
       </c>
-      <c r="E14" s="33" t="n">
-        <v>5.71</v>
-      </c>
       <c r="F14" s="34" t="n">
-        <v>4.8</v>
+        <v>5.04</v>
       </c>
       <c r="G14" s="34" t="n">
-        <v>5.89</v>
+        <v>5.72</v>
       </c>
       <c r="H14" s="35">
         <f>D14-E14</f>
